--- a/docs/qa/MetaCheck_Test_Plan.xlsx
+++ b/docs/qa/MetaCheck_Test_Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dovydenkovmihail/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47358EF9-FDFA-E445-8677-C2C40E5D9922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F064461E-93C3-C444-9E7C-166E52F65B81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="17120" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17080" yWindow="680" windowWidth="17120" windowHeight="19920" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Обзор плана тестирования" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="257">
   <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
     <t>Project Name</t>
   </si>
   <si>
@@ -418,12 +412,6 @@
     <t>Контроль версий</t>
   </si>
   <si>
-    <t>Format</t>
-  </si>
-  <si>
-    <t>File Name</t>
-  </si>
-  <si>
     <t>XLSX</t>
   </si>
   <si>
@@ -763,18 +751,12 @@
     <t>Отчет о тестировании</t>
   </si>
   <si>
-    <t>MetaCheck_отчет о тестировании.docx</t>
-  </si>
-  <si>
     <t>Тест план</t>
   </si>
   <si>
     <t>Работы</t>
   </si>
   <si>
-    <t>MetaCheck_тест_кейс.xlsx</t>
-  </si>
-  <si>
     <t>Подробный тест кейс</t>
   </si>
   <si>
@@ -794,6 +776,24 @@
   </si>
   <si>
     <t>Примечания</t>
+  </si>
+  <si>
+    <t>Поле</t>
+  </si>
+  <si>
+    <t>Значение</t>
+  </si>
+  <si>
+    <t>Формат</t>
+  </si>
+  <si>
+    <t>Имя Файла</t>
+  </si>
+  <si>
+    <t>MetaCheck_Test_Cases.xlsx</t>
+  </si>
+  <si>
+    <t>MetaCheck_Test_Summary_Report.docx</t>
   </si>
 </sst>
 </file>
@@ -934,17 +934,17 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1256,79 +1256,79 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>202</v>
+      <c r="A1" s="11" t="s">
+        <v>198</v>
       </c>
       <c r="B1" s="12"/>
     </row>
     <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>203</v>
+      <c r="A3" s="15" t="s">
+        <v>199</v>
       </c>
       <c r="B3" s="12"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>210</v>
+      <c r="A11" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="B11" s="12"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="55" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>6</v>
+      <c r="A13" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="B13" s="12"/>
     </row>
@@ -1342,161 +1342,175 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="12"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="12"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="12"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="B21" s="12"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="12"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="B22" s="12"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B21" s="12"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="B23" s="12"/>
+    </row>
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" s="12"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B27" s="12"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B22" s="12"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
+      <c r="B28" s="12"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="12"/>
-    </row>
-    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="B25" s="12"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B27" s="12"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+      <c r="B29" s="12"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="12"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
+      <c r="B30" s="12"/>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B29" s="12"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
+      <c r="B31" s="12"/>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="12"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
+      <c r="B32" s="12"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="12"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+      <c r="B33" s="12"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="12"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B33" s="12"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
+      <c r="B35" s="12"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="12"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
+      <c r="B36" s="12"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="12"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
+      <c r="B37" s="12"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" s="12"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="12"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
+      <c r="B40" s="12"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="12"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="B39" s="12"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
+      <c r="B41" s="12"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B40" s="12"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
+      <c r="B42" s="12"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="12"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
+      <c r="B43" s="12"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="12"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
+      <c r="B44" s="12"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" s="13" t="s">
         <v>26</v>
-      </c>
-      <c r="B43" s="12"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="12"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="B45" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="A13:B15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A35:B35"/>
@@ -1512,20 +1526,6 @@
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A13:B15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1545,7 +1545,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1553,8 +1553,8 @@
       <c r="E1" s="12"/>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>217</v>
+      <c r="A3" s="15" t="s">
+        <v>213</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -1563,160 +1563,160 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="70" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="56" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="56" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="70" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="70" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="70" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="70" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="42" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
-        <v>222</v>
+      <c r="A14" s="15" t="s">
+        <v>218</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1724,77 +1724,77 @@
     </row>
     <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>66</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
-        <v>227</v>
+      <c r="A21" s="15" t="s">
+        <v>223</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -1802,8 +1802,8 @@
       <c r="E21" s="12"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
-        <v>229</v>
+      <c r="A23" s="14" t="s">
+        <v>225</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
@@ -1811,8 +1811,8 @@
       <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>73</v>
+      <c r="A24" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
@@ -1820,8 +1820,8 @@
       <c r="E24" s="12"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>74</v>
+      <c r="A25" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
@@ -1829,8 +1829,8 @@
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>75</v>
+      <c r="A26" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -1838,8 +1838,8 @@
       <c r="E26" s="12"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>76</v>
+      <c r="A27" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -1847,8 +1847,8 @@
       <c r="E27" s="12"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>77</v>
+      <c r="A28" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -1856,8 +1856,8 @@
       <c r="E28" s="12"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
-        <v>228</v>
+      <c r="A30" s="14" t="s">
+        <v>224</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
@@ -1865,8 +1865,8 @@
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>78</v>
+      <c r="A31" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -1874,8 +1874,8 @@
       <c r="E31" s="12"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
-        <v>79</v>
+      <c r="A32" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
@@ -1883,8 +1883,8 @@
       <c r="E32" s="12"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="11" t="s">
-        <v>80</v>
+      <c r="A33" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -1892,8 +1892,8 @@
       <c r="E33" s="12"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
-        <v>81</v>
+      <c r="A34" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -1901,8 +1901,8 @@
       <c r="E34" s="12"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>82</v>
+      <c r="A35" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
@@ -1910,8 +1910,8 @@
       <c r="E35" s="12"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>83</v>
+      <c r="A36" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -1919,69 +1919,78 @@
       <c r="E36" s="12"/>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="17" t="s">
-        <v>230</v>
+      <c r="A38" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="28" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A35:E35"/>
@@ -1989,16 +1998,7 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A24:E24"/>
     <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A28:E28"/>
     <mergeCell ref="A36:E36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2019,7 +2019,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2027,300 +2027,300 @@
       <c r="E1" s="12"/>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>235</v>
+      <c r="A3" s="15" t="s">
+        <v>231</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
     </row>
-    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
-        <v>241</v>
+      <c r="A14" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>115</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>118</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>124</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
-        <v>244</v>
+      <c r="A23" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>132</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2349,7 +2349,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.2">
       <c r="A1" s="18" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -2358,8 +2358,8 @@
       <c r="F1" s="12"/>
     </row>
     <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
-        <v>136</v>
+      <c r="A3" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2369,399 +2369,399 @@
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F5" s="8"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F8" s="8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F11" s="8"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F14" s="8"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F16" s="8"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F17" s="8"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F18" s="8"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F19" s="8"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F20" s="8"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F21" s="8"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F22" s="8"/>
     </row>
     <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F23" s="8"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F24" s="8"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F25" s="8"/>
     </row>
